--- a/Apostas_Diarias/Apostas_20260408.xlsx
+++ b/Apostas_Diarias/Apostas_20260408.xlsx
@@ -136,6 +136,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Apostas_Diarias/Apostas_20260408.xlsx
+++ b/Apostas_Diarias/Apostas_20260408.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B590F4F950649877B3BD0305B1510344D07F14F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB065BEB-2895-46E2-87CB-EE95C59114EB}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_2B590F4F958646613503DAF0503BA0306083E7E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCBC690C-B200-4AC5-AB3B-040FDE13F7D0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="34">
   <si>
     <t>Data</t>
   </si>
@@ -71,6 +71,54 @@
     <t>2026-04-08</t>
   </si>
   <si>
+    <t>P1 ⭐</t>
+  </si>
+  <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>TURKEY 2</t>
+  </si>
+  <si>
+    <t>Serik Belediyespor x Van Buyuksehir Belediyespor</t>
+  </si>
+  <si>
+    <t>Lay_CS_0x1_B365</t>
+  </si>
+  <si>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>ITALY 3</t>
+  </si>
+  <si>
+    <t>Juventus B x Ternana</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>Inter Milan (Res) x A.C. Trento S.C.S.D.</t>
+  </si>
+  <si>
+    <t>12:50:00</t>
+  </si>
+  <si>
+    <t>SAUDI ARABIA 1</t>
+  </si>
+  <si>
+    <t>Al-Anwar Club x Al-Wahda (KSA)</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>GREECE 1</t>
+  </si>
+  <si>
+    <t>Atromitos x Kifisia</t>
+  </si>
+  <si>
     <t>P2</t>
   </si>
   <si>
@@ -83,7 +131,10 @@
     <t>Goztepe x Galatasaray</t>
   </si>
   <si>
-    <t>Lay_CS_0x1_B365</t>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>Lay_CS_1x0_B365</t>
   </si>
 </sst>
 </file>
@@ -136,10 +187,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -427,13 +474,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -476,9 +524,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -488,26 +533,24 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2">
-        <v>8.8000000000000007</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>8.8000000000000007</v>
+        <v>25</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -516,13 +559,376 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
+        <v>19.479166666666668</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3">
+        <v>24</v>
+      </c>
+      <c r="H3">
+        <v>24</v>
+      </c>
+      <c r="I3">
+        <v>500</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J11" si="0">IF(L3=1,"GREEN","RED")</f>
+        <v>GREEN</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K11" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>20.326086956521742</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>26</v>
+      </c>
+      <c r="H4">
+        <v>26</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="1"/>
+        <v>18.700000000000003</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="H5">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>57.01219512195123</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H6">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I6">
+        <v>500</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
         <v>59.935897435897431</v>
       </c>
-      <c r="L2">
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>500</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>38.958333333333336</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8">
+        <v>13.5</v>
+      </c>
+      <c r="H8">
+        <v>13.5</v>
+      </c>
+      <c r="I8">
+        <v>500</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>37.400000000000006</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>12</v>
+      </c>
+      <c r="H9">
+        <v>12</v>
+      </c>
+      <c r="I9">
+        <v>500</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>42.5</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>500</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>51.944444444444443</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>11.5</v>
+      </c>
+      <c r="H11">
+        <v>11.5</v>
+      </c>
+      <c r="I11">
+        <v>500</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L11">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K11">
+    <sortCondition ref="E2:E11"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>